--- a/Book1/B1_Companion_Workbook.xlsx
+++ b/Book1/B1_Companion_Workbook.xlsx
@@ -1229,7 +1229,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1237,7 +1237,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Risk by process step—before and after action</a:t>
             </a:r>
@@ -1596,7 +1596,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1651,7 +1651,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1683,7 +1683,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
           <a:r>
@@ -1724,7 +1724,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1732,7 +1732,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Trigger rule outcome</a:t>
             </a:r>
@@ -1812,7 +1812,7 @@
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
@@ -1838,7 +1838,7 @@
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
@@ -1862,7 +1862,7 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1930,7 +1930,7 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
           <a:r>
@@ -1971,7 +1971,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1979,7 +1979,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Failure modes by severity band</a:t>
             </a:r>
@@ -2126,7 +2126,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -2181,7 +2181,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -2226,7 +2226,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -2234,7 +2234,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Actions by hierarchy level (1 strongest)</a:t>
             </a:r>
@@ -2387,7 +2387,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -2442,7 +2442,7 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C24" s="66" t="inlineStr">
         <is>
-          <t>19 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
     <row r="9" ht="15" customHeight="1" s="55">
       <c r="B9" s="140" t="inlineStr">
         <is>
-          <t>Document code: NF-CW1 · Identity: NBSM v1.0 · Baseline: EBL-3.1 · Issued 19 August 2026</t>
+          <t>Document code: NF-CW1 · Identity: NBSM v1.0 · Baseline: EBL-3.1 · Issued 22 August 2026</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10906,7 @@
       <c r="C13" s="64" t="n"/>
       <c r="D13" s="82" t="inlineStr">
         <is>
-          <t>v1.0  ·  issued 19 August 2026</t>
+          <t>v1.0  ·  issued 22 August 2026</t>
         </is>
       </c>
       <c r="E13" s="64" t="n"/>
@@ -11278,7 +11278,7 @@
     <row r="26" ht="15" customHeight="1" s="55">
       <c r="A26" s="90" t="inlineStr">
         <is>
-          <t>The Norwood Files · Companion to Book One · v1.0 · issued 19 August 2026 · matches the first edition (Editorial Baseline EBL-2)</t>
+          <t>The Norwood Files · Companion to Book One · v1.0 · issued 22 August 2026 · matches the first edition (Editorial Baseline EBL-3.1)</t>
         </is>
       </c>
     </row>
